--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20261012.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20261012.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>8,564,000</t>
+          <t>40,513,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>40,513,000</t>
+          <t>8,564,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
